--- a/AAII_Financials/Yearly/EAF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/EAF_YR_FIN.xlsx
@@ -1011,7 +1011,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="3">
-        <v>15000</v>
+        <v>-3400</v>
       </c>
       <c r="F14" s="3">
         <v>171100</v>
@@ -1131,7 +1131,7 @@
         <v>577800</v>
       </c>
       <c r="E17" s="3">
-        <v>599300</v>
+        <v>617700</v>
       </c>
       <c r="F17" s="3">
         <v>667600</v>
@@ -1182,7 +1182,7 @@
         <v>-73700</v>
       </c>
       <c r="E18" s="3">
-        <v>-60600</v>
+        <v>-79000</v>
       </c>
       <c r="F18" s="3">
         <v>-47100</v>
@@ -1305,7 +1305,7 @@
         <v>-11400</v>
       </c>
       <c r="E21" s="3">
-        <v>3600</v>
+        <v>-14800</v>
       </c>
       <c r="F21" s="3">
         <v>8900</v>
